--- a/OMOP Analysis/Results/Output_yearly_costs_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_costs_OMOP-Adjusted.xlsx
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>635.04</v>
+        <v>523.46</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -431,28 +431,28 @@
         <v>8960.83</v>
       </c>
       <c r="E2">
-        <v>595.99</v>
+        <v>592.66</v>
       </c>
       <c r="F2">
-        <v>476.76</v>
+        <v>366.36</v>
       </c>
       <c r="G2">
-        <v>224.76</v>
+        <v>80.39</v>
       </c>
       <c r="H2">
-        <v>861.46</v>
+        <v>756</v>
       </c>
       <c r="I2">
-        <v>14275</v>
+        <v>17315</v>
       </c>
       <c r="J2">
-        <v>4.988281048403688</v>
+        <v>4.5</v>
       </c>
       <c r="K2">
-        <v>625.2623197025613</v>
+        <v>514.63</v>
       </c>
       <c r="L2">
-        <v>644.8176802974386</v>
+        <v>532.29</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>361.97</v>
+        <v>299.04</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6332.79</v>
+        <v>6341.47</v>
       </c>
       <c r="E3">
-        <v>517.15</v>
+        <v>490.11</v>
       </c>
       <c r="F3">
-        <v>168</v>
+        <v>42.06</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>542.39</v>
+        <v>445.49</v>
       </c>
       <c r="I3">
-        <v>14275</v>
+        <v>17315</v>
       </c>
       <c r="J3">
-        <v>4.328410785721182</v>
+        <v>3.72</v>
       </c>
       <c r="K3">
-        <v>353.4857513283438</v>
+        <v>291.74</v>
       </c>
       <c r="L3">
-        <v>370.4542486716563</v>
+        <v>306.34</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>654.01</v>
+        <v>676.16</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>8960.83</v>
+        <v>9299.690000000001</v>
       </c>
       <c r="E2">
-        <v>594.48</v>
+        <v>633.9400000000001</v>
       </c>
       <c r="F2">
-        <v>500.39</v>
+        <v>504</v>
       </c>
       <c r="G2">
         <v>252</v>
       </c>
       <c r="H2">
-        <v>882</v>
+        <v>908.02</v>
       </c>
       <c r="I2">
-        <v>13861</v>
+        <v>13863</v>
       </c>
       <c r="J2">
-        <v>5.049402218682347</v>
+        <v>5.38</v>
       </c>
       <c r="K2">
-        <v>644.1124891803676</v>
+        <v>665.61</v>
       </c>
       <c r="L2">
-        <v>663.9075108196324</v>
+        <v>686.71</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>372.78</v>
+        <v>386.3</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6332.79</v>
+        <v>10159.2</v>
       </c>
       <c r="E3">
-        <v>520.96</v>
+        <v>554.48</v>
       </c>
       <c r="F3">
-        <v>183.59</v>
+        <v>187.45</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>546.37</v>
+        <v>563.39</v>
       </c>
       <c r="I3">
-        <v>13861</v>
+        <v>13863</v>
       </c>
       <c r="J3">
-        <v>4.424937053971126</v>
+        <v>4.71</v>
       </c>
       <c r="K3">
-        <v>364.1065253051478</v>
+        <v>377.07</v>
       </c>
       <c r="L3">
-        <v>381.4534746948521</v>
+        <v>395.53</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_costs_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_costs_OMOP-Adjusted.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>523.46</v>
+        <v>577.5700000000001</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>8960.83</v>
+        <v>9614.440000000001</v>
       </c>
       <c r="E2">
-        <v>592.66</v>
+        <v>619.95</v>
       </c>
       <c r="F2">
-        <v>366.36</v>
+        <v>427.41</v>
       </c>
       <c r="G2">
-        <v>80.39</v>
+        <v>103.2</v>
       </c>
       <c r="H2">
-        <v>756</v>
+        <v>830.24</v>
       </c>
       <c r="I2">
-        <v>17315</v>
+        <v>22538</v>
       </c>
       <c r="J2">
-        <v>4.5</v>
+        <v>4.13</v>
       </c>
       <c r="K2">
-        <v>514.63</v>
+        <v>569.48</v>
       </c>
       <c r="L2">
-        <v>532.29</v>
+        <v>585.66</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>299.04</v>
+        <v>321.14</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,7 +469,7 @@
         <v>6341.47</v>
       </c>
       <c r="E3">
-        <v>490.11</v>
+        <v>510.22</v>
       </c>
       <c r="F3">
         <v>42.06</v>
@@ -478,19 +478,19 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>445.49</v>
+        <v>488.98</v>
       </c>
       <c r="I3">
-        <v>17315</v>
+        <v>22538</v>
       </c>
       <c r="J3">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>291.74</v>
+        <v>314.48</v>
       </c>
       <c r="L3">
-        <v>306.34</v>
+        <v>327.8</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>676.16</v>
+        <v>749.2</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9299.690000000001</v>
+        <v>9614.440000000001</v>
       </c>
       <c r="E2">
-        <v>633.9400000000001</v>
+        <v>652.54</v>
       </c>
       <c r="F2">
-        <v>504</v>
+        <v>584.39</v>
       </c>
       <c r="G2">
-        <v>252</v>
+        <v>315.44</v>
       </c>
       <c r="H2">
-        <v>908.02</v>
+        <v>983.04</v>
       </c>
       <c r="I2">
-        <v>13863</v>
+        <v>17944</v>
       </c>
       <c r="J2">
-        <v>5.38</v>
+        <v>4.87</v>
       </c>
       <c r="K2">
-        <v>665.61</v>
+        <v>739.65</v>
       </c>
       <c r="L2">
-        <v>686.71</v>
+        <v>758.75</v>
       </c>
     </row>
     <row r="3">
@@ -608,7 +608,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>386.3</v>
+        <v>416.86</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -617,28 +617,28 @@
         <v>10159.2</v>
       </c>
       <c r="E3">
-        <v>554.48</v>
+        <v>575.3099999999999</v>
       </c>
       <c r="F3">
-        <v>187.45</v>
+        <v>224.26</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>563.39</v>
+        <v>620.0700000000001</v>
       </c>
       <c r="I3">
-        <v>13863</v>
+        <v>17944</v>
       </c>
       <c r="J3">
-        <v>4.71</v>
+        <v>4.29</v>
       </c>
       <c r="K3">
-        <v>377.07</v>
+        <v>408.44</v>
       </c>
       <c r="L3">
-        <v>395.53</v>
+        <v>425.28</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_costs_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_costs_OMOP-Adjusted.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>577.5700000000001</v>
+        <v>3082.9</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9614.440000000001</v>
+        <v>45876.35</v>
       </c>
       <c r="E2">
-        <v>619.95</v>
+        <v>2908.37</v>
       </c>
       <c r="F2">
-        <v>427.41</v>
+        <v>2317.68</v>
       </c>
       <c r="G2">
-        <v>103.2</v>
+        <v>1183.97</v>
       </c>
       <c r="H2">
-        <v>830.24</v>
+        <v>4065.23</v>
       </c>
       <c r="I2">
-        <v>22538</v>
+        <v>18143</v>
       </c>
       <c r="J2">
-        <v>4.13</v>
+        <v>21.59</v>
       </c>
       <c r="K2">
-        <v>569.48</v>
+        <v>3040.58</v>
       </c>
       <c r="L2">
-        <v>585.66</v>
+        <v>3125.22</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>321.14</v>
+        <v>1737.55</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6341.47</v>
+        <v>40636.82</v>
       </c>
       <c r="E3">
-        <v>510.22</v>
+        <v>2528.24</v>
       </c>
       <c r="F3">
-        <v>42.06</v>
+        <v>836.46</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>488.98</v>
+        <v>2525.11</v>
       </c>
       <c r="I3">
-        <v>22538</v>
+        <v>18143</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>18.77</v>
       </c>
       <c r="K3">
-        <v>314.48</v>
+        <v>1700.76</v>
       </c>
       <c r="L3">
-        <v>327.8</v>
+        <v>1774.34</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>749.2</v>
+        <v>2702.42</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9614.440000000001</v>
+        <v>65948.36</v>
       </c>
       <c r="E2">
-        <v>652.54</v>
+        <v>2746.69</v>
       </c>
       <c r="F2">
-        <v>584.39</v>
+        <v>1954.68</v>
       </c>
       <c r="G2">
-        <v>315.44</v>
+        <v>983.26</v>
       </c>
       <c r="H2">
-        <v>983.04</v>
+        <v>3521.98</v>
       </c>
       <c r="I2">
-        <v>17944</v>
+        <v>17954</v>
       </c>
       <c r="J2">
-        <v>4.87</v>
+        <v>20.5</v>
       </c>
       <c r="K2">
-        <v>739.65</v>
+        <v>2662.24</v>
       </c>
       <c r="L2">
-        <v>758.75</v>
+        <v>2742.6</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>416.86</v>
+        <v>1549.01</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>10159.2</v>
+        <v>63543.1</v>
       </c>
       <c r="E3">
-        <v>575.3099999999999</v>
+        <v>2379.9</v>
       </c>
       <c r="F3">
-        <v>224.26</v>
+        <v>722.86</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>620.0700000000001</v>
+        <v>2206.43</v>
       </c>
       <c r="I3">
-        <v>17944</v>
+        <v>17954</v>
       </c>
       <c r="J3">
-        <v>4.29</v>
+        <v>17.76</v>
       </c>
       <c r="K3">
-        <v>408.44</v>
+        <v>1514.2</v>
       </c>
       <c r="L3">
-        <v>425.28</v>
+        <v>1583.82</v>
       </c>
     </row>
   </sheetData>
